--- a/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 4,06</t>
+          <t>-10,33; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,51</t>
+          <t>0,74; 18,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 11,22</t>
+          <t>-1,5; 10,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 13,51</t>
+          <t>1,24; 13,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,43</t>
+          <t>-3,73; 5,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,37</t>
+          <t>2,33; 12,63</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,05; 57,55</t>
+          <t>-68,52; 67,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 232,0</t>
+          <t>0,88; 264,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 513,8</t>
+          <t>-31,95; 445,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 581,04</t>
+          <t>4,59; 607,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 109,9</t>
+          <t>-36,59; 104,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 217,11</t>
+          <t>20,51; 230,46</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,54</t>
+          <t>-2,83; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,03</t>
+          <t>-0,31; 9,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 8,65</t>
+          <t>-2,26; 8,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 11,23</t>
+          <t>-1,1; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,94</t>
+          <t>-0,51; 5,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,24</t>
+          <t>1,12; 8,54</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 644,58</t>
+          <t>-60,64; 621,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 1110,95</t>
+          <t>-26,98; 1011,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 508,72</t>
+          <t>-42,69; 562,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 766,55</t>
+          <t>-30,08; 733,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 336,9</t>
+          <t>-20,62; 321,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 435,95</t>
+          <t>9,27; 434,19</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,77</t>
+          <t>-0,89; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 10,88</t>
+          <t>-0,59; 10,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,1</t>
+          <t>-3,18; 2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 14,55</t>
+          <t>1,95; 15,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,23</t>
+          <t>-1,36; 4,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,26</t>
+          <t>2,13; 11,01</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,75; —</t>
+          <t>-77,58; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; —</t>
+          <t>-30,66; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,26; 750,51</t>
+          <t>-70,07; 668,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,85; 1615,01</t>
+          <t>50,91; 2014,28</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,64</t>
+          <t>-0,95; 3,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,35</t>
+          <t>1,77; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,52</t>
+          <t>-4,71; 0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,47</t>
+          <t>-1,08; 5,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,23</t>
+          <t>-1,96; 1,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,51</t>
+          <t>1,41; 6,2</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 530,36</t>
+          <t>-44,61; 616,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,18; 1158,96</t>
+          <t>51,39; 1112,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,5; 58,24</t>
+          <t>-90,85; 41,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 344,99</t>
+          <t>-26,77; 277,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,0; 73,86</t>
+          <t>-61,45; 71,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,68; 382,37</t>
+          <t>35,6; 338,04</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,18</t>
+          <t>-5,65; 0,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,2</t>
+          <t>-3,75; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,84</t>
+          <t>-1,39; 3,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,87</t>
+          <t>-0,81; 4,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,99</t>
+          <t>-2,68; 0,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,5</t>
+          <t>-1,66; 2,48</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,79</t>
+          <t>-100,0; 73,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 179,86</t>
+          <t>-71,15; 240,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,97; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,29; 90,05</t>
+          <t>-87,02; 64,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 220,37</t>
+          <t>-54,29; 205,71</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 6,23</t>
+          <t>-2,99; 6,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 9,39</t>
+          <t>-1,0; 9,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 3,09</t>
+          <t>-6,58; 2,99</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 7,16</t>
+          <t>-4,25; 7,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,18</t>
+          <t>-4,17; 3,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 6,67</t>
+          <t>-1,51; 6,67</t>
         </is>
       </c>
     </row>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,66; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-85,96; 469,77</t>
+          <t>-84,61; 407,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 671,17</t>
+          <t>-46,78; 658,93</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,92</t>
+          <t>-1,62; 1,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,96</t>
+          <t>2,37; 6,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,1</t>
+          <t>-0,96; 2,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,67</t>
+          <t>1,99; 5,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,46</t>
+          <t>-0,7; 1,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,5</t>
+          <t>2,63; 5,42</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 75,47</t>
+          <t>-37,79; 67,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>53,85; 241,94</t>
+          <t>52,84; 258,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 93,13</t>
+          <t>-26,42; 97,08</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41,63; 259,06</t>
+          <t>45,62; 257,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 54,79</t>
+          <t>-19,37; 55,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>74,11; 203,5</t>
+          <t>69,04; 205,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 4,34</t>
+          <t>-10,55; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 18,23</t>
+          <t>-0,41; 17,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 10,87</t>
+          <t>-1,58; 10,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 13,46</t>
+          <t>1,17; 13,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 5,69</t>
+          <t>-3,79; 6,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 12,63</t>
+          <t>2,11; 12,63</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,52; 67,65</t>
+          <t>-66,93; 67,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 264,37</t>
+          <t>-2,81; 238,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 445,46</t>
+          <t>-33,19; 491,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 607,91</t>
+          <t>3,45; 689,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 104,49</t>
+          <t>-35,42; 114,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,51; 230,46</t>
+          <t>17,81; 245,52</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,89</t>
+          <t>-2,35; 6,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 9,59</t>
+          <t>-0,27; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 8,13</t>
+          <t>-1,5; 8,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 10,29</t>
+          <t>-1,49; 10,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,96</t>
+          <t>-0,45; 5,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,54</t>
+          <t>0,78; 8,27</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 621,97</t>
+          <t>-61,2; 734,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 1011,28</t>
+          <t>-22,76; 1563,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 562,68</t>
+          <t>-33,72; 673,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 733,84</t>
+          <t>-29,41; 760,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 321,95</t>
+          <t>-15,69; 358,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 434,19</t>
+          <t>7,27; 417,05</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 9,45</t>
+          <t>-0,9; 9,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 10,73</t>
+          <t>-0,47; 12,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,06</t>
+          <t>-3,53; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 15,12</t>
+          <t>1,67; 15,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,02</t>
+          <t>-1,35; 4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,01</t>
+          <t>1,81; 10,87</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,58; —</t>
+          <t>-73,74; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,66; —</t>
+          <t>-14,15; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,07; 668,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,91; 2014,28</t>
+          <t>41,49; 1931,23</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,61</t>
+          <t>-0,71; 3,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,19</t>
+          <t>1,47; 8,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,4</t>
+          <t>-4,17; 0,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,97</t>
+          <t>-0,31; 6,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,23</t>
+          <t>-2,18; 1,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,2</t>
+          <t>1,37; 6,52</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 616,86</t>
+          <t>-43,59; 657,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,39; 1112,65</t>
+          <t>35,69; 1046,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,85; 41,5</t>
+          <t>-89,92; 42,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 277,71</t>
+          <t>-14,62; 291,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 71,05</t>
+          <t>-63,2; 69,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,6; 338,04</t>
+          <t>35,88; 402,42</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,26</t>
+          <t>-5,6; 0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,53</t>
+          <t>-3,97; 2,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,05</t>
+          <t>-1,43; 2,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,09</t>
+          <t>-0,74; 4,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,62</t>
+          <t>-2,79; 0,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,48</t>
+          <t>-1,59; 2,56</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,58</t>
+          <t>-100,0; 58,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 240,18</t>
+          <t>-71,85; 188,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,02; 64,54</t>
+          <t>-84,02; 109,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,29; 205,71</t>
+          <t>-54,48; 225,28</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,4</t>
+          <t>-3,39; 5,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 9,29</t>
+          <t>-1,04; 9,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,99</t>
+          <t>-7,12; 3,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 7,29</t>
+          <t>-4,85; 7,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,14</t>
+          <t>-3,56; 3,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,67</t>
+          <t>-1,96; 6,1</t>
         </is>
       </c>
     </row>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-88,66; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-84,61; 407,33</t>
+          <t>-81,7; 485,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 658,93</t>
+          <t>-52,66; 628,25</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,78</t>
+          <t>-1,52; 1,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,66</t>
+          <t>2,28; 6,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,1</t>
+          <t>-1,03; 2,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,87</t>
+          <t>2,0; 5,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,44</t>
+          <t>-0,73; 1,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,42</t>
+          <t>2,7; 5,48</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 67,85</t>
+          <t>-34,88; 65,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>52,84; 258,71</t>
+          <t>46,22; 248,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 97,08</t>
+          <t>-27,81; 98,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45,62; 257,08</t>
+          <t>49,71; 271,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 55,28</t>
+          <t>-19,8; 61,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>69,04; 205,23</t>
+          <t>70,89; 213,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Clase-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-3,01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,85</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>7,93</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 4,31</t>
+          <t>-1,89; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 17,59</t>
+          <t>0,69; 13,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 10,78</t>
+          <t>-11,1; 4,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,49</t>
+          <t>0,7; 18,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,08</t>
+          <t>-3,86; 6,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 12,63</t>
+          <t>2,1; 12,82</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>100,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>152,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-26,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>100,35%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151,12%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 67,75</t>
+          <t>-33,24; 513,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 238,23</t>
+          <t>-0,78; 582,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 491,12</t>
+          <t>-69,05; 57,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 689,62</t>
+          <t>0,51; 238,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 114,09</t>
+          <t>-36,56; 109,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 245,52</t>
+          <t>16,72; 225,43</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,3</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,3</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,54</t>
+          <t>-1,59; 8,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 9,94</t>
+          <t>-1,12; 11,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,71</t>
+          <t>-2,19; 6,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,32</t>
+          <t>-0,52; 10,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,83</t>
+          <t>-0,94; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,27</t>
+          <t>0,61; 8,26</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>67,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>153,17%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88,56%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118,73%</t>
+          <t>155,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>132,58%</t>
+          <t>128,62%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 734,8</t>
+          <t>-39,22; 508,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 1563,47</t>
+          <t>-31,86; 742,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 673,16</t>
+          <t>-59,72; 644,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 760,72</t>
+          <t>-36,7; 1120,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 358,05</t>
+          <t>-20,89; 336,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 417,05</t>
+          <t>0,42; 424,52</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,64</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,88</t>
+          <t>-3,24; 2,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 12,05</t>
+          <t>1,98; 14,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,14</t>
+          <t>-0,92; 9,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,1</t>
+          <t>-0,67; 10,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,48</t>
+          <t>-1,25; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,87</t>
+          <t>2,24; 11,28</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-41,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>457,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>192,15%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>252,26%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-41,44%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459,57%</t>
+          <t>239,13%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>363,39%</t>
+          <t>349,32%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,74; —</t>
+          <t>1,36; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1032,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,15; —</t>
+          <t>-73,13; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,26; 750,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,49; 1931,23</t>
+          <t>33,13; 1619,68</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,97</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>4,57</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,92</t>
+          <t>-4,63; 0,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,38</t>
+          <t>-0,35; 6,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,35</t>
+          <t>-0,96; 3,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,3</t>
+          <t>3,17; 10,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,1</t>
+          <t>-2,13; 1,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,52</t>
+          <t>2,46; 7,55</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-57,92%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>77,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>310,97%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-57,92%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>411,85%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148,73%</t>
+          <t>180,4%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 657,54</t>
+          <t>-89,5; 58,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,69; 1046,85</t>
+          <t>-10,06; 361,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,92; 42,98</t>
+          <t>-49,98; 530,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 291,99</t>
+          <t>103,94; 1453,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 69,41</t>
+          <t>-61,0; 73,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,88; 402,42</t>
+          <t>68,35; 457,04</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-2,4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,36</t>
+          <t>-1,4; 2,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,94</t>
+          <t>-0,69; 3,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,94</t>
+          <t>-5,5; 0,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,22</t>
+          <t>-3,84; 3,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,91</t>
+          <t>-2,73; 0,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,56</t>
+          <t>-1,45; 2,49</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>60,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>136,19%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-69,58%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-9,97%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>60,87%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136,03%</t>
+          <t>-9,69%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-71,85; 188,33</t>
+          <t>-79,57; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 81,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,91; 178,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-84,02; 109,27</t>
+          <t>-86,29; 90,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,48; 225,28</t>
+          <t>-47,99; 228,84</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3,87</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>1,95</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 5,47</t>
+          <t>-7,31; 3,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,11</t>
+          <t>-5,81; 4,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,25</t>
+          <t>-3,34; 6,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 7,11</t>
+          <t>-0,51; 9,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,52</t>
+          <t>-4,14; 3,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,1</t>
+          <t>-2,32; 5,95</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-41,59%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>113,36%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>260,76%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-41,59%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>269,29%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1507,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,7; 485,69</t>
+          <t>-85,96; 469,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 628,25</t>
+          <t>-60,01; 588,94</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3,66</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,18</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>4,33</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,76</t>
+          <t>-1,07; 2,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,78</t>
+          <t>1,69; 5,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,02</t>
+          <t>-1,38; 1,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,77</t>
+          <t>2,81; 7,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,53</t>
+          <t>-0,72; 1,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,48</t>
+          <t>3,04; 5,73</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>124,71%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>130,42%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>128,76%</t>
+          <t>147,73%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>128,95%</t>
+          <t>136,12%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 65,62</t>
+          <t>-29,61; 93,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>46,22; 248,18</t>
+          <t>41,25; 251,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 98,78</t>
+          <t>-33,87; 75,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49,71; 271,39</t>
+          <t>61,52; 263,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 61,71</t>
+          <t>-20,3; 54,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,89; 213,79</t>
+          <t>78,78; 214,39</t>
         </is>
       </c>
     </row>
